--- a/data/trans_orig/IP07A14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>47302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62111</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>37242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45564</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>59218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26286</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -2357,47 +2357,47 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5294</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>591</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56031</t>
+          <t>56545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68250</t>
+          <t>68108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>100225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121225</t>
+          <t>120764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>40449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>50830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71330</t>
+          <t>71021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27252</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>39051</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40505</t>
+          <t>40080</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52675</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87662</t>
+          <t>89379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>49237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26095</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41160</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>155342</t>
+          <t>156724</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>182579</t>
+          <t>183534</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>188517</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>216549</t>
+          <t>216641</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>354554</t>
+          <t>352616</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>392522</t>
+          <t>391958</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>99537</t>
+          <t>98752</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>127638</t>
+          <t>125706</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>97483</t>
+          <t>98115</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>125008</t>
+          <t>125978</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>203059</t>
+          <t>204785</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>241772</t>
+          <t>244096</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22995</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43519</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55817</t>
+          <t>55675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51627</t>
+          <t>51130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49781</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64315</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57470</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73428</t>
+          <t>73072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112065</t>
+          <t>112916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133606</t>
+          <t>134466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>44361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>38712</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77436</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97042</t>
+          <t>97577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>34839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46703</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>66713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>422</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45595</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>174101</t>
+          <t>176226</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>202884</t>
+          <t>204313</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>188717</t>
+          <t>189573</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>215885</t>
+          <t>215677</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>372344</t>
+          <t>372813</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>413952</t>
+          <t>412062</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96212</t>
+          <t>94805</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>122772</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>81912</t>
+          <t>81196</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107591</t>
+          <t>108185</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>183126</t>
+          <t>184794</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>222891</t>
+          <t>222788</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69214</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27947</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>30649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61886</t>
+          <t>62574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79597</t>
+          <t>79977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>61708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130537</t>
+          <t>128446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152896</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27897</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38564</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55399</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77006</t>
+          <t>77953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>38984</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>52907</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>84623</t>
+          <t>84906</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103582</t>
+          <t>104015</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>57076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52129</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>198799</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>228563</t>
+          <t>227614</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>212892</t>
+          <t>210464</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>240998</t>
+          <t>239732</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>418671</t>
+          <t>419728</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>461429</t>
+          <t>461732</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>94786</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124155</t>
+          <t>122456</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89927</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>117387</t>
+          <t>119013</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>193550</t>
+          <t>194539</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>235374</t>
+          <t>235278</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
